--- a/2026/2DE MAYO/Junio/2DEDMAYO-JUNIO.xlsx
+++ b/2026/2DE MAYO/Junio/2DEDMAYO-JUNIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\2DE MAYO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F70C6C-5916-4E89-997A-B2AC33B6A53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFA353E-FFFC-4A67-8AD0-7030591E5575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="137">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -417,12 +417,6 @@
     <t xml:space="preserve">Honorarios administracion Junio </t>
   </si>
   <si>
-    <t>Transf 06/05</t>
-  </si>
-  <si>
-    <t>Seguros Integral de Consorcio BERKLEY INTERNATIONAL SEGUROS S.A. Poliza N° 13-228546 - ULTIMO MES</t>
-  </si>
-  <si>
     <t>VTO 17/07</t>
   </si>
   <si>
@@ -445,6 +439,9 @@
   </si>
   <si>
     <t>Ingreso a fondo comun de inversion</t>
+  </si>
+  <si>
+    <t>Seguros Integral de Consorcio BERKLEY INTERNATIONAL SEGUROS S.A. Poliza N° 13-228546 - LA POLIZA SE DEBITA LOS PRIMEROS DIAS DE JULIO</t>
   </si>
 </sst>
 </file>
@@ -462,7 +459,7 @@
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -638,13 +635,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1263,7 +1253,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1372,7 +1362,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1472,7 +1461,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="22" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="22" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1499,12 +1487,6 @@
     <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1516,6 +1498,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="12" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="18" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="18" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1528,125 +1555,26 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="18" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="16" fontId="18" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1656,20 +1584,79 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="12" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2085,11 +2072,11 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="176" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
+      <c r="B1" s="166" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
       <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2103,12 +2090,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="177" t="s">
+      <c r="B3" s="169" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="178"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="170"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -2126,7 +2113,7 @@
         <v>111</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="52" t="s">
@@ -2136,7 +2123,7 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2146,49 +2133,49 @@
       <c r="E6" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="180" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="180"/>
+      <c r="B8" s="172" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="172"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="180"/>
-      <c r="C9" s="180"/>
+      <c r="B9" s="172"/>
+      <c r="C9" s="172"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="180"/>
-      <c r="C10" s="180"/>
+      <c r="B10" s="172"/>
+      <c r="C10" s="172"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="179" t="s">
+      <c r="A13" s="171" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="179"/>
-      <c r="C13" s="179"/>
-      <c r="D13" s="179"/>
-      <c r="E13" s="179"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="171"/>
+      <c r="D13" s="171"/>
+      <c r="E13" s="171"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="179"/>
-      <c r="B14" s="179"/>
-      <c r="C14" s="179"/>
-      <c r="D14" s="179"/>
-      <c r="E14" s="179"/>
+      <c r="A14" s="171"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="171"/>
+      <c r="D14" s="171"/>
+      <c r="E14" s="171"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="179"/>
-      <c r="B15" s="179"/>
-      <c r="C15" s="179"/>
-      <c r="D15" s="179"/>
-      <c r="E15" s="179"/>
+      <c r="A15" s="171"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="171"/>
+      <c r="D15" s="171"/>
+      <c r="E15" s="171"/>
     </row>
     <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="179"/>
-      <c r="B16" s="179"/>
-      <c r="C16" s="179"/>
-      <c r="D16" s="179"/>
-      <c r="E16" s="179"/>
+      <c r="A16" s="171"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="171"/>
+      <c r="D16" s="171"/>
+      <c r="E16" s="171"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2218,10 +2205,10 @@
         <v>88</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C22" s="5"/>
-      <c r="D22" s="141">
+      <c r="D22" s="139">
         <v>1899703.78</v>
       </c>
       <c r="E22" s="5"/>
@@ -2232,7 +2219,7 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="141">
+      <c r="D23" s="139">
         <v>-470176.69</v>
       </c>
       <c r="E23" s="5"/>
@@ -2243,7 +2230,7 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="141">
+      <c r="D24" s="139">
         <v>0.91</v>
       </c>
       <c r="E24" s="5"/>
@@ -2254,11 +2241,11 @@
       </c>
       <c r="B25" s="44"/>
       <c r="C25" s="44"/>
-      <c r="D25" s="142">
+      <c r="D25" s="140">
         <f>SUM(D22:D24)</f>
         <v>1429528</v>
       </c>
-      <c r="E25" s="89"/>
+      <c r="E25" s="88"/>
       <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2267,21 +2254,21 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="141"/>
+      <c r="D26" s="139"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="23"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="141"/>
+      <c r="D27" s="139"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="141"/>
+      <c r="D28" s="139"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2290,7 +2277,7 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="161">
+      <c r="D29" s="213">
         <v>184800</v>
       </c>
       <c r="E29" s="5"/>
@@ -2301,11 +2288,11 @@
       </c>
       <c r="B30" s="44"/>
       <c r="C30" s="44"/>
-      <c r="D30" s="143">
+      <c r="D30" s="141">
         <f>SUM(D26:D29)</f>
         <v>184800</v>
       </c>
-      <c r="E30" s="89"/>
+      <c r="E30" s="88"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
@@ -2313,8 +2300,8 @@
       </c>
       <c r="B31" s="24"/>
       <c r="C31" s="24"/>
-      <c r="D31" s="144"/>
-      <c r="E31" s="90">
+      <c r="D31" s="142"/>
+      <c r="E31" s="89">
         <f>D25+D30</f>
         <v>1614328</v>
       </c>
@@ -2326,28 +2313,28 @@
       </c>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
-      <c r="D32" s="145"/>
-      <c r="E32" s="91"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="90"/>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="172" t="s">
+      <c r="A33" s="167" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="173"/>
+      <c r="B33" s="168"/>
       <c r="C33" s="41"/>
-      <c r="D33" s="162">
+      <c r="D33" s="139">
         <v>45000</v>
       </c>
-      <c r="E33" s="92" t="s">
+      <c r="E33" s="91" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="172"/>
-      <c r="B34" s="173"/>
+      <c r="A34" s="167"/>
+      <c r="B34" s="168"/>
       <c r="C34" s="41"/>
-      <c r="D34" s="159"/>
-      <c r="E34" s="92"/>
+      <c r="D34" s="214"/>
+      <c r="E34" s="91"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="24" t="s">
@@ -2355,8 +2342,8 @@
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
-      <c r="D35" s="154"/>
-      <c r="E35" s="93">
+      <c r="D35" s="152"/>
+      <c r="E35" s="92">
         <f>SUM(D33:D34)</f>
         <v>45000</v>
       </c>
@@ -2367,28 +2354,24 @@
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
-      <c r="D36" s="155"/>
-      <c r="E36" s="94"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="93"/>
     </row>
     <row r="37" spans="1:7" s="30" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="181" t="s">
-        <v>129</v>
-      </c>
-      <c r="B37" s="182"/>
+      <c r="A37" s="173" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="174"/>
       <c r="C37" s="42"/>
-      <c r="D37" s="216">
-        <v>65251.97</v>
-      </c>
-      <c r="E37" s="174" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="183"/>
-      <c r="B38" s="184"/>
+      <c r="D37" s="215"/>
+      <c r="E37" s="164"/>
+    </row>
+    <row r="38" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="175"/>
+      <c r="B38" s="176"/>
       <c r="C38" s="42"/>
-      <c r="D38" s="217"/>
-      <c r="E38" s="175"/>
+      <c r="D38" s="216"/>
+      <c r="E38" s="165"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
@@ -2396,20 +2379,20 @@
       </c>
       <c r="B39" s="24"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="154"/>
+      <c r="D39" s="152"/>
       <c r="E39" s="58">
         <f>SUM(D37:D38)</f>
-        <v>65251.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="95"/>
-      <c r="C40" s="95"/>
-      <c r="D40" s="156"/>
-      <c r="E40" s="147"/>
+      <c r="B40" s="94"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="154"/>
+      <c r="E40" s="145"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
@@ -2417,26 +2400,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="41"/>
-      <c r="D41" s="160">
+      <c r="D41" s="144">
         <v>701906.85</v>
       </c>
-      <c r="E41" s="99" t="s">
+      <c r="E41" s="98" t="s">
         <v>121</v>
       </c>
       <c r="G41" s="77"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>98</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="160">
+      <c r="D42" s="144">
         <v>54804.85</v>
       </c>
-      <c r="E42" s="99" t="s">
+      <c r="E42" s="98" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2449,10 +2432,10 @@
         <v>97</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="160">
+      <c r="D43" s="144">
         <v>101643.56</v>
       </c>
-      <c r="E43" s="100" t="str">
+      <c r="E43" s="99" t="str">
         <f>E42</f>
         <v>Debito 12/06</v>
       </c>
@@ -2466,10 +2449,10 @@
         <v>96</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="160">
+      <c r="D44" s="144">
         <v>6089.43</v>
       </c>
-      <c r="E44" s="101" t="str">
+      <c r="E44" s="100" t="str">
         <f>E43</f>
         <v>Debito 12/06</v>
       </c>
@@ -2478,9 +2461,9 @@
       <c r="A45" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="95"/>
-      <c r="C45" s="95"/>
-      <c r="D45" s="157"/>
+      <c r="B45" s="94"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="155"/>
       <c r="E45" s="58">
         <f>SUM(D41:D44)</f>
         <v>864444.69000000006</v>
@@ -2490,10 +2473,10 @@
       <c r="A46" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="95"/>
-      <c r="C46" s="95"/>
-      <c r="D46" s="156"/>
-      <c r="E46" s="147"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="94"/>
+      <c r="D46" s="154"/>
+      <c r="E46" s="145"/>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
@@ -2501,23 +2484,23 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="160">
+      <c r="D47" s="144">
         <v>371485.85</v>
       </c>
-      <c r="E47" s="99" t="s">
+      <c r="E47" s="98" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="128" t="s">
+      <c r="A48" s="127" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="129"/>
+      <c r="B48" s="128"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="160">
+      <c r="D48" s="144">
         <v>355959.47</v>
       </c>
-      <c r="E48" s="99" t="s">
+      <c r="E48" s="98" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2527,7 +2510,7 @@
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="24"/>
-      <c r="D49" s="158"/>
+      <c r="D49" s="156"/>
       <c r="E49" s="58">
         <f>SUM(D47:D48)</f>
         <v>727445.32</v>
@@ -2537,48 +2520,48 @@
       <c r="A50" s="27"/>
       <c r="B50" s="24"/>
       <c r="C50" s="24"/>
-      <c r="D50" s="154"/>
-      <c r="E50" s="148"/>
+      <c r="D50" s="152"/>
+      <c r="E50" s="146"/>
     </row>
     <row r="51" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="102" t="s">
+      <c r="A51" s="101" t="s">
         <v>94</v>
       </c>
-      <c r="B51" s="98"/>
+      <c r="B51" s="97"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="160">
+      <c r="D51" s="144">
         <v>17700.11</v>
       </c>
-      <c r="E51" s="99" t="s">
+      <c r="E51" s="98" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="102" t="s">
+      <c r="A52" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="98"/>
+      <c r="B52" s="97"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="160">
+      <c r="D52" s="144">
         <v>105000</v>
       </c>
-      <c r="E52" s="137" t="s">
+      <c r="E52" s="136" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="168"/>
-      <c r="B53" s="169"/>
+      <c r="A53" s="177"/>
+      <c r="B53" s="178"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="146"/>
-      <c r="E53" s="137"/>
+      <c r="D53" s="144"/>
+      <c r="E53" s="136"/>
     </row>
     <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="102"/>
-      <c r="B54" s="98"/>
+      <c r="A54" s="101"/>
+      <c r="B54" s="97"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="146"/>
-      <c r="E54" s="136"/>
+      <c r="D54" s="144"/>
+      <c r="E54" s="135"/>
     </row>
     <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="24" t="s">
@@ -2587,7 +2570,7 @@
       <c r="B55" s="27"/>
       <c r="C55" s="27"/>
       <c r="D55" s="26"/>
-      <c r="E55" s="149">
+      <c r="E55" s="147">
         <f>SUM(D51:D54)</f>
         <v>122700.11</v>
       </c>
@@ -2598,8 +2581,8 @@
       </c>
       <c r="B56" s="49"/>
       <c r="C56" s="24"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="96"/>
+      <c r="D56" s="142"/>
+      <c r="E56" s="95"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
@@ -2607,10 +2590,10 @@
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="160">
+      <c r="D57" s="144">
         <v>69000</v>
       </c>
-      <c r="E57" s="97"/>
+      <c r="E57" s="96"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
@@ -2618,8 +2601,9 @@
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="160">
-        <v>64674.37</v>
+      <c r="D58" s="144">
+        <f>64674.37+1741</f>
+        <v>66415.37</v>
       </c>
       <c r="E58" s="31"/>
     </row>
@@ -2632,7 +2616,7 @@
       <c r="D59" s="63"/>
       <c r="E59" s="58">
         <f>SUM(D57:D58)</f>
-        <v>133674.37</v>
+        <v>135415.37</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2650,7 +2634,8 @@
       <c r="C61" s="25"/>
       <c r="D61" s="65"/>
       <c r="E61" s="66">
-        <v>0</v>
+        <f>4095718.96-3509333.49</f>
+        <v>586385.46999999974</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2668,9 +2653,9 @@
       <c r="D63" s="69"/>
       <c r="E63" s="70">
         <f>(SUM(E28:E61))</f>
-        <v>3572844.46</v>
-      </c>
-      <c r="F63" s="88"/>
+        <v>4095718.9599999995</v>
+      </c>
+      <c r="F63" s="87"/>
       <c r="G63" s="33"/>
       <c r="H63" s="77"/>
       <c r="I63" s="77"/>
@@ -2690,7 +2675,7 @@
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D65" s="67"/>
       <c r="E65" s="67"/>
-      <c r="H65" s="103"/>
+      <c r="H65" s="102"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
@@ -2702,22 +2687,22 @@
       <c r="E66" s="72"/>
     </row>
     <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="168"/>
-      <c r="B67" s="169"/>
+      <c r="A67" s="177"/>
+      <c r="B67" s="178"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="80"/>
+      <c r="D67" s="61"/>
       <c r="E67" s="59"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="168"/>
-      <c r="B68" s="169"/>
+      <c r="A68" s="177"/>
+      <c r="B68" s="178"/>
       <c r="C68" s="5"/>
       <c r="D68" s="61"/>
       <c r="E68" s="59"/>
     </row>
     <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="172"/>
-      <c r="B69" s="173"/>
+      <c r="A69" s="167"/>
+      <c r="B69" s="168"/>
       <c r="C69" s="5"/>
       <c r="D69" s="61"/>
       <c r="E69" s="59"/>
@@ -2733,47 +2718,56 @@
       <c r="A71" s="38"/>
       <c r="B71" s="37"/>
       <c r="C71" s="37"/>
-      <c r="D71" s="45"/>
+      <c r="D71" s="217"/>
       <c r="E71" s="45">
         <f>SUM(D67:D70)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="73" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D72" s="67"/>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="67"/>
+    </row>
     <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="138" t="s">
+      <c r="A74" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="B74" s="139"/>
-      <c r="C74" s="139"/>
-      <c r="D74" s="140"/>
-      <c r="E74" s="150">
+      <c r="B74" s="138"/>
+      <c r="C74" s="138"/>
+      <c r="D74" s="218"/>
+      <c r="E74" s="148">
         <v>120000</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D75" s="67"/>
+    </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B76" s="9"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
+      <c r="D76" s="69"/>
       <c r="E76" s="50">
         <f>E71+E74</f>
         <v>120000</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D77" s="67"/>
+    </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="55" t="s">
         <v>13</v>
       </c>
       <c r="B78" s="56">
         <f>E63</f>
-        <v>3572844.46</v>
-      </c>
+        <v>4095718.9599999995</v>
+      </c>
+      <c r="D78" s="67"/>
     </row>
     <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="55" t="s">
@@ -2781,8 +2775,9 @@
       </c>
       <c r="B79" s="56">
         <f>E63-E61</f>
-        <v>3572844.46</v>
-      </c>
+        <v>3509333.4899999998</v>
+      </c>
+      <c r="D79" s="67"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="55" t="s">
@@ -2792,6 +2787,7 @@
         <f>E76-E74</f>
         <v>0</v>
       </c>
+      <c r="D80" s="67"/>
     </row>
     <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="55" t="s">
@@ -2801,77 +2797,89 @@
         <f>E76</f>
         <v>120000</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="D81" s="67"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D82" s="67"/>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D83" s="67"/>
+    </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="163" t="s">
+      <c r="A84" s="157" t="s">
         <v>105</v>
       </c>
-      <c r="B84" s="164">
+      <c r="B84" s="158">
         <v>615184.62</v>
       </c>
+      <c r="D84" s="67"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="130" t="s">
+      <c r="A85" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="B85" s="131">
+      <c r="B85" s="130">
         <f>PRORRATEO!G38</f>
         <v>400000</v>
       </c>
       <c r="C85" s="22"/>
+      <c r="D85" s="67"/>
       <c r="E85" s="78"/>
       <c r="F85" s="79"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="152" t="s">
+      <c r="A86" s="150" t="s">
         <v>125</v>
       </c>
-      <c r="B86" s="151">
+      <c r="B86" s="149">
         <v>-5837</v>
       </c>
       <c r="C86" s="22"/>
+      <c r="D86" s="67"/>
       <c r="E86" s="78"/>
       <c r="F86" s="79"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="167" t="s">
+      <c r="A87" s="161" t="s">
         <v>126</v>
       </c>
-      <c r="B87" s="151">
+      <c r="B87" s="149">
         <v>-16000</v>
       </c>
       <c r="C87" s="22"/>
+      <c r="D87" s="67"/>
       <c r="E87" s="78"/>
       <c r="F87" s="79"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="167" t="s">
+      <c r="A88" s="161" t="s">
         <v>127</v>
       </c>
-      <c r="B88" s="151">
+      <c r="B88" s="149">
         <v>-133100</v>
       </c>
       <c r="C88" s="22"/>
+      <c r="D88" s="67"/>
       <c r="E88" s="78"/>
       <c r="F88" s="79"/>
     </row>
     <row r="89" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="165" t="s">
+      <c r="A89" s="159" t="s">
         <v>118</v>
       </c>
-      <c r="B89" s="166">
+      <c r="B89" s="160">
         <v>-130100</v>
       </c>
-      <c r="C89" s="129"/>
+      <c r="C89" s="128"/>
+      <c r="D89" s="67"/>
       <c r="E89" s="78"/>
       <c r="F89" s="79"/>
     </row>
     <row r="90" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="132" t="s">
+      <c r="A90" s="131" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="133">
+      <c r="B90" s="132">
         <f>SUM(B84:C89)</f>
         <v>730147.62</v>
       </c>
@@ -2884,10 +2892,10 @@
       <c r="D91"/>
     </row>
     <row r="92" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="81" t="s">
+      <c r="A92" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="B92" s="82">
+      <c r="B92" s="81">
         <v>1575550.6</v>
       </c>
       <c r="C92" s="29"/>
@@ -2897,25 +2905,26 @@
       <c r="A93" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="B93" s="86">
+      <c r="B93" s="85">
         <f>-B79</f>
-        <v>-3572844.46</v>
-      </c>
+        <v>-3509333.4899999998</v>
+      </c>
+      <c r="E93" s="33"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B94" s="86">
+      <c r="B94" s="85">
         <f>-B80</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="B95" s="86">
+        <v>134</v>
+      </c>
+      <c r="B95" s="85">
         <v>-1600000</v>
       </c>
     </row>
@@ -2923,7 +2932,7 @@
       <c r="A96" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B96" s="86">
+      <c r="B96" s="85">
         <f>B106</f>
         <v>0</v>
       </c>
@@ -2932,46 +2941,46 @@
       <c r="A97" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B97" s="87">
+      <c r="B97" s="86">
         <f>PRORRATEO!G37</f>
-        <v>3557376.2300000009</v>
+        <v>3847604.5700000008</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="84" t="s">
+      <c r="A98" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B98" s="85">
+      <c r="B98" s="84">
         <f>SUM(B92:C97)</f>
-        <v>-39917.629999998957</v>
+        <v>313821.6800000011</v>
       </c>
       <c r="D98" s="32"/>
       <c r="E98" s="33"/>
     </row>
     <row r="99" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="83"/>
-      <c r="B99" s="83"/>
+      <c r="A99" s="82"/>
+      <c r="B99" s="82"/>
     </row>
     <row r="100" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="220" t="s">
-        <v>137</v>
-      </c>
-      <c r="B100" s="221">
+      <c r="A100" s="162" t="s">
+        <v>135</v>
+      </c>
+      <c r="B100" s="163">
         <v>1600000</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="171" t="s">
+      <c r="A102" s="180" t="s">
         <v>26</v>
       </c>
-      <c r="B102" s="171"/>
-      <c r="C102" s="171"/>
+      <c r="B102" s="180"/>
+      <c r="C102" s="180"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="171"/>
-      <c r="B103" s="171"/>
-      <c r="C103" s="171"/>
+      <c r="A103" s="180"/>
+      <c r="B103" s="180"/>
+      <c r="C103" s="180"/>
     </row>
     <row r="104" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="74"/>
@@ -2979,13 +2988,13 @@
       <c r="C104" s="28">
         <v>40000</v>
       </c>
-      <c r="E104" s="88"/>
+      <c r="E104" s="87"/>
     </row>
     <row r="105" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="74"/>
       <c r="B105" s="76"/>
       <c r="C105" s="73"/>
-      <c r="D105" s="88"/>
+      <c r="D105" s="87"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
@@ -3001,35 +3010,41 @@
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="170"/>
-      <c r="B108" s="170"/>
-      <c r="C108" s="170"/>
-      <c r="D108" s="170"/>
-      <c r="E108" s="170"/>
+      <c r="A108" s="179"/>
+      <c r="B108" s="179"/>
+      <c r="C108" s="179"/>
+      <c r="D108" s="179"/>
+      <c r="E108" s="179"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="170"/>
-      <c r="B109" s="170"/>
-      <c r="C109" s="170"/>
-      <c r="D109" s="170"/>
-      <c r="E109" s="170"/>
+      <c r="A109" s="179"/>
+      <c r="B109" s="179"/>
+      <c r="C109" s="179"/>
+      <c r="D109" s="179"/>
+      <c r="E109" s="179"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="170"/>
-      <c r="B110" s="170"/>
-      <c r="C110" s="170"/>
-      <c r="D110" s="170"/>
-      <c r="E110" s="170"/>
+      <c r="A110" s="179"/>
+      <c r="B110" s="179"/>
+      <c r="C110" s="179"/>
+      <c r="D110" s="179"/>
+      <c r="E110" s="179"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="170"/>
-      <c r="B111" s="170"/>
-      <c r="C111" s="170"/>
-      <c r="D111" s="170"/>
-      <c r="E111" s="170"/>
+      <c r="A111" s="179"/>
+      <c r="B111" s="179"/>
+      <c r="C111" s="179"/>
+      <c r="D111" s="179"/>
+      <c r="E111" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A108:E111"/>
+    <mergeCell ref="A102:C103"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A69:B69"/>
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="E37:E38"/>
     <mergeCell ref="B1:D1"/>
@@ -3039,12 +3054,6 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A37:B38"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A108:E111"/>
-    <mergeCell ref="A102:C103"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A69:B69"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3080,16 +3089,16 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="185"/>
-      <c r="N1" s="185"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
       <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3098,24 +3107,24 @@
       <c r="C2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="211">
-        <v>0</v>
-      </c>
-      <c r="E2" s="211"/>
+      <c r="D2" s="185">
+        <v>0</v>
+      </c>
+      <c r="E2" s="185"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="211"/>
-      <c r="I2" s="211"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="M2" s="210">
+      <c r="M2" s="184">
         <f>Q2</f>
         <v>4095718.96</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="184"/>
       <c r="O2" s="43"/>
       <c r="P2" s="21"/>
       <c r="Q2">
@@ -3140,204 +3149,204 @@
       <c r="O3" s="46"/>
     </row>
     <row r="4" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="194" t="str">
+      <c r="A4" s="200" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
-      <c r="K4" s="195"/>
-      <c r="L4" s="195"/>
-      <c r="M4" s="195"/>
-      <c r="N4" s="195"/>
-      <c r="O4" s="196"/>
+      <c r="B4" s="201"/>
+      <c r="C4" s="201"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="201"/>
+      <c r="L4" s="201"/>
+      <c r="M4" s="201"/>
+      <c r="N4" s="201"/>
+      <c r="O4" s="202"/>
     </row>
     <row r="5" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="197"/>
-      <c r="B5" s="198"/>
-      <c r="C5" s="198"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="198"/>
-      <c r="G5" s="198"/>
-      <c r="H5" s="198"/>
-      <c r="I5" s="198"/>
-      <c r="J5" s="198"/>
-      <c r="K5" s="198"/>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="198"/>
-      <c r="O5" s="199"/>
+      <c r="A5" s="203"/>
+      <c r="B5" s="204"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="204"/>
+      <c r="F5" s="204"/>
+      <c r="G5" s="204"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="204"/>
+      <c r="J5" s="204"/>
+      <c r="K5" s="204"/>
+      <c r="L5" s="204"/>
+      <c r="M5" s="204"/>
+      <c r="N5" s="204"/>
+      <c r="O5" s="205"/>
     </row>
     <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="197"/>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
-      <c r="D6" s="198"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="198"/>
-      <c r="G6" s="198"/>
-      <c r="H6" s="198"/>
-      <c r="I6" s="198"/>
-      <c r="J6" s="198"/>
-      <c r="K6" s="198"/>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="198"/>
-      <c r="O6" s="199"/>
+      <c r="A6" s="203"/>
+      <c r="B6" s="204"/>
+      <c r="C6" s="204"/>
+      <c r="D6" s="204"/>
+      <c r="E6" s="204"/>
+      <c r="F6" s="204"/>
+      <c r="G6" s="204"/>
+      <c r="H6" s="204"/>
+      <c r="I6" s="204"/>
+      <c r="J6" s="204"/>
+      <c r="K6" s="204"/>
+      <c r="L6" s="204"/>
+      <c r="M6" s="204"/>
+      <c r="N6" s="204"/>
+      <c r="O6" s="205"/>
     </row>
     <row r="7" spans="1:18" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="198"/>
-      <c r="H7" s="198"/>
-      <c r="I7" s="198"/>
-      <c r="J7" s="198"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="198"/>
-      <c r="O7" s="199"/>
+      <c r="A7" s="203"/>
+      <c r="B7" s="204"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="204"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="204"/>
+      <c r="H7" s="204"/>
+      <c r="I7" s="204"/>
+      <c r="J7" s="204"/>
+      <c r="K7" s="204"/>
+      <c r="L7" s="204"/>
+      <c r="M7" s="204"/>
+      <c r="N7" s="204"/>
+      <c r="O7" s="205"/>
     </row>
     <row r="8" spans="1:18" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="200"/>
-      <c r="B8" s="201"/>
-      <c r="C8" s="201"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="201"/>
-      <c r="F8" s="201"/>
-      <c r="G8" s="201"/>
-      <c r="H8" s="201"/>
-      <c r="I8" s="201"/>
-      <c r="J8" s="201"/>
-      <c r="K8" s="201"/>
-      <c r="L8" s="201"/>
-      <c r="M8" s="201"/>
-      <c r="N8" s="201"/>
-      <c r="O8" s="202"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="207"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="207"/>
+      <c r="G8" s="207"/>
+      <c r="H8" s="207"/>
+      <c r="I8" s="207"/>
+      <c r="J8" s="207"/>
+      <c r="K8" s="207"/>
+      <c r="L8" s="207"/>
+      <c r="M8" s="207"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="208"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="186" t="s">
+      <c r="A9" s="192" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="188" t="s">
+      <c r="B9" s="186" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="188" t="s">
+      <c r="C9" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="125"/>
-      <c r="E9" s="188" t="s">
+      <c r="D9" s="124"/>
+      <c r="E9" s="186" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="186" t="s">
+      <c r="F9" s="192" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="188" t="s">
+      <c r="G9" s="186" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="188" t="s">
+      <c r="H9" s="186" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="190" t="s">
+      <c r="I9" s="196" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="186" t="s">
+      <c r="J9" s="192" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="186" t="s">
+      <c r="K9" s="192" t="s">
         <v>112</v>
       </c>
-      <c r="L9" s="186" t="s">
+      <c r="L9" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="192" t="s">
+      <c r="M9" s="198" t="s">
         <v>48</v>
       </c>
       <c r="N9" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="O9" s="205" t="s">
+      <c r="O9" s="210" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="203"/>
-      <c r="B10" s="204"/>
-      <c r="C10" s="189"/>
-      <c r="D10" s="126"/>
-      <c r="E10" s="189"/>
-      <c r="F10" s="187"/>
-      <c r="G10" s="189"/>
-      <c r="H10" s="204"/>
-      <c r="I10" s="191"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
-      <c r="L10" s="187"/>
-      <c r="M10" s="193"/>
+      <c r="A10" s="209"/>
+      <c r="B10" s="187"/>
+      <c r="C10" s="195"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="195"/>
+      <c r="F10" s="193"/>
+      <c r="G10" s="195"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="193"/>
+      <c r="K10" s="193"/>
+      <c r="L10" s="193"/>
+      <c r="M10" s="199"/>
       <c r="N10" s="47" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="O10" s="206"/>
+      <c r="O10" s="211"/>
     </row>
     <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="104"/>
-      <c r="E11" s="123">
+      <c r="D11" s="103"/>
+      <c r="E11" s="122">
         <v>6.18</v>
       </c>
-      <c r="F11" s="106">
+      <c r="F11" s="105">
         <v>253115.01</v>
       </c>
-      <c r="G11" s="218">
+      <c r="G11" s="151">
         <f>F11</f>
         <v>253115.01</v>
       </c>
-      <c r="H11" s="107" t="s">
+      <c r="H11" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="108">
+      <c r="I11" s="107">
         <f t="shared" ref="I11:I35" si="0">F11-G11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="108">
+      <c r="J11" s="107">
         <f>IF(I11&gt;0,I11*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="108"/>
-      <c r="L11" s="109">
+      <c r="K11" s="107"/>
+      <c r="L11" s="108">
         <f>M$2*E11/100</f>
         <v>253115.43172799997</v>
       </c>
-      <c r="M11" s="110">
+      <c r="M11" s="109">
         <f>D$2*E11/100</f>
         <v>0</v>
       </c>
-      <c r="N11" s="111">
+      <c r="N11" s="110">
         <f t="shared" ref="N11:N35" si="1">ROUND(SUM(I11:M11),0) + P11</f>
         <v>253115.01</v>
       </c>
-      <c r="O11" s="112">
+      <c r="O11" s="111">
         <f t="shared" ref="O11:O35" si="2">ROUND(N11*3%,0) + N11</f>
         <v>260708.01</v>
       </c>
@@ -3347,52 +3356,52 @@
       <c r="Q11" s="33"/>
     </row>
     <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="104" t="s">
+      <c r="B12" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="104" t="s">
+      <c r="D12" s="103" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="123">
+      <c r="E12" s="122">
         <v>4.33</v>
       </c>
-      <c r="F12" s="106">
+      <c r="F12" s="105">
         <v>172033.02</v>
       </c>
-      <c r="G12" s="219">
+      <c r="G12" s="113">
         <v>177194.02</v>
       </c>
-      <c r="H12" s="107" t="s">
+      <c r="H12" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="108">
+      <c r="I12" s="107">
         <f t="shared" si="0"/>
         <v>-5161</v>
       </c>
-      <c r="J12" s="108">
+      <c r="J12" s="107">
         <f t="shared" ref="J12:J35" si="3">IF(I12&gt;0,I12*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="108"/>
-      <c r="L12" s="109">
+      <c r="K12" s="107"/>
+      <c r="L12" s="108">
         <f t="shared" ref="L12:L35" si="4">M$2*E12/100</f>
         <v>177344.63096799998</v>
       </c>
-      <c r="M12" s="110">
+      <c r="M12" s="109">
         <f t="shared" ref="M12:M35" si="5">D$2*E12/100</f>
         <v>0</v>
       </c>
-      <c r="N12" s="111">
+      <c r="N12" s="110">
         <f t="shared" si="1"/>
         <v>172184.02</v>
       </c>
-      <c r="O12" s="112">
+      <c r="O12" s="111">
         <f t="shared" si="2"/>
         <v>177350.02</v>
       </c>
@@ -3403,50 +3412,50 @@
       <c r="Q12" s="33"/>
     </row>
     <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="113" t="s">
+      <c r="B13" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="113" t="s">
+      <c r="C13" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="113"/>
-      <c r="E13" s="124">
+      <c r="D13" s="112"/>
+      <c r="E13" s="123">
         <v>6.18</v>
       </c>
-      <c r="F13" s="114">
+      <c r="F13" s="113">
         <v>252358.03</v>
       </c>
-      <c r="G13" s="219">
+      <c r="G13" s="113">
         <v>260000.03</v>
       </c>
-      <c r="H13" s="107" t="s">
+      <c r="H13" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="108">
+      <c r="I13" s="107">
         <f t="shared" si="0"/>
         <v>-7642</v>
       </c>
-      <c r="J13" s="108">
+      <c r="J13" s="107">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K13" s="108"/>
-      <c r="L13" s="109">
+      <c r="K13" s="107"/>
+      <c r="L13" s="108">
         <f t="shared" si="4"/>
         <v>253115.43172799997</v>
       </c>
-      <c r="M13" s="110">
+      <c r="M13" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N13" s="111">
+      <c r="N13" s="110">
         <f t="shared" si="1"/>
         <v>245473.03</v>
       </c>
-      <c r="O13" s="112">
+      <c r="O13" s="111">
         <f t="shared" si="2"/>
         <v>252837.03</v>
       </c>
@@ -3457,51 +3466,51 @@
       <c r="Q13" s="32"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="104" t="s">
+      <c r="B14" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="104"/>
-      <c r="E14" s="123">
+      <c r="D14" s="103"/>
+      <c r="E14" s="122">
         <v>4.33</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="105">
         <v>171869.04</v>
       </c>
-      <c r="G14" s="219">
+      <c r="G14" s="113">
         <f>F14</f>
         <v>171869.04</v>
       </c>
-      <c r="H14" s="107" t="s">
+      <c r="H14" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="108">
+      <c r="I14" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="108">
+      <c r="J14" s="107">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="108"/>
-      <c r="L14" s="109">
+      <c r="K14" s="107"/>
+      <c r="L14" s="108">
         <f t="shared" si="4"/>
         <v>177344.63096799998</v>
       </c>
-      <c r="M14" s="110">
+      <c r="M14" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N14" s="111">
+      <c r="N14" s="110">
         <f t="shared" si="1"/>
         <v>177345.04</v>
       </c>
-      <c r="O14" s="112">
+      <c r="O14" s="111">
         <f t="shared" si="2"/>
         <v>182665.04</v>
       </c>
@@ -3512,52 +3521,52 @@
       <c r="R14" s="33"/>
     </row>
     <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="104" t="s">
+      <c r="D15" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="123">
+      <c r="E15" s="122">
         <v>6.18</v>
       </c>
-      <c r="F15" s="106">
+      <c r="F15" s="105">
         <v>253115.05</v>
       </c>
-      <c r="G15" s="219">
+      <c r="G15" s="113">
         <v>261000</v>
       </c>
-      <c r="H15" s="107" t="s">
+      <c r="H15" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="108">
+      <c r="I15" s="107">
         <f t="shared" si="0"/>
         <v>-7884.9500000000116</v>
       </c>
-      <c r="J15" s="108">
+      <c r="J15" s="107">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K15" s="108"/>
-      <c r="L15" s="109">
+      <c r="K15" s="107"/>
+      <c r="L15" s="108">
         <f t="shared" si="4"/>
         <v>253115.43172799997</v>
       </c>
-      <c r="M15" s="110">
+      <c r="M15" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N15" s="111">
+      <c r="N15" s="110">
         <f t="shared" si="1"/>
         <v>245230.05</v>
       </c>
-      <c r="O15" s="112">
+      <c r="O15" s="111">
         <f t="shared" si="2"/>
         <v>252587.05</v>
       </c>
@@ -3568,50 +3577,50 @@
       <c r="R15" s="33"/>
     </row>
     <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="104" t="s">
+      <c r="A16" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="104"/>
-      <c r="E16" s="123">
+      <c r="D16" s="103"/>
+      <c r="E16" s="122">
         <v>4.33</v>
       </c>
-      <c r="F16" s="106">
+      <c r="F16" s="105">
         <v>172029.06</v>
       </c>
-      <c r="G16" s="219">
+      <c r="G16" s="113">
         <v>177190.06</v>
       </c>
-      <c r="H16" s="107" t="s">
+      <c r="H16" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="108">
+      <c r="I16" s="107">
         <f t="shared" si="0"/>
         <v>-5161</v>
       </c>
-      <c r="J16" s="108">
+      <c r="J16" s="107">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K16" s="108"/>
-      <c r="L16" s="109">
+      <c r="K16" s="107"/>
+      <c r="L16" s="108">
         <f t="shared" si="4"/>
         <v>177344.63096799998</v>
       </c>
-      <c r="M16" s="110">
+      <c r="M16" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N16" s="111">
+      <c r="N16" s="110">
         <f t="shared" si="1"/>
         <v>172184.06</v>
       </c>
-      <c r="O16" s="112">
+      <c r="O16" s="111">
         <f t="shared" si="2"/>
         <v>177350.06</v>
       </c>
@@ -3621,51 +3630,51 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="104" t="s">
+      <c r="A17" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="104"/>
-      <c r="E17" s="123">
+      <c r="D17" s="103"/>
+      <c r="E17" s="122">
         <v>6.18</v>
       </c>
-      <c r="F17" s="106">
+      <c r="F17" s="105">
         <v>247507.07</v>
       </c>
-      <c r="G17" s="219">
+      <c r="G17" s="113">
         <f>290000-G32</f>
         <v>258339.78</v>
       </c>
-      <c r="H17" s="107" t="s">
+      <c r="H17" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="108">
+      <c r="I17" s="107">
         <f t="shared" si="0"/>
         <v>-10832.709999999992</v>
       </c>
-      <c r="J17" s="108">
+      <c r="J17" s="107">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="108"/>
-      <c r="L17" s="109">
+      <c r="K17" s="107"/>
+      <c r="L17" s="108">
         <f t="shared" si="4"/>
         <v>253115.43172799997</v>
       </c>
-      <c r="M17" s="110">
+      <c r="M17" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="111">
+      <c r="N17" s="110">
         <f t="shared" si="1"/>
         <v>242283.07</v>
       </c>
-      <c r="O17" s="112">
+      <c r="O17" s="111">
         <f t="shared" si="2"/>
         <v>249551.07</v>
       </c>
@@ -3675,51 +3684,51 @@
       </c>
     </row>
     <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="104" t="s">
+      <c r="C18" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="104"/>
-      <c r="E18" s="123">
+      <c r="D18" s="103"/>
+      <c r="E18" s="122">
         <v>4.33</v>
       </c>
-      <c r="F18" s="106">
+      <c r="F18" s="105">
         <v>177345.08</v>
       </c>
-      <c r="G18" s="219">
+      <c r="G18" s="113">
         <f>F18</f>
         <v>177345.08</v>
       </c>
-      <c r="H18" s="107" t="s">
+      <c r="H18" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="108">
+      <c r="I18" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="108">
+      <c r="J18" s="107">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K18" s="108"/>
-      <c r="L18" s="109">
+      <c r="K18" s="107"/>
+      <c r="L18" s="108">
         <f t="shared" si="4"/>
         <v>177344.63096799998</v>
       </c>
-      <c r="M18" s="110">
+      <c r="M18" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N18" s="111">
+      <c r="N18" s="110">
         <f t="shared" si="1"/>
         <v>177345.08</v>
       </c>
-      <c r="O18" s="112">
+      <c r="O18" s="111">
         <f t="shared" si="2"/>
         <v>182665.08</v>
       </c>
@@ -3729,54 +3738,54 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="104" t="s">
+      <c r="A19" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="104" t="s">
+      <c r="B19" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="104" t="s">
+      <c r="C19" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="104"/>
-      <c r="E19" s="123">
+      <c r="D19" s="103"/>
+      <c r="E19" s="122">
         <v>6.18</v>
       </c>
-      <c r="F19" s="106">
+      <c r="F19" s="105">
         <v>348548.09</v>
       </c>
-      <c r="G19" s="219">
+      <c r="G19" s="113">
         <f>400000-G33</f>
         <v>368339.78</v>
       </c>
-      <c r="H19" s="107" t="s">
+      <c r="H19" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="I19" s="108">
+      <c r="I19" s="107">
         <f t="shared" si="0"/>
         <v>-19791.690000000002</v>
       </c>
-      <c r="J19" s="108">
+      <c r="J19" s="107">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K19" s="108">
+      <c r="K19" s="107">
         <f>80000+27000</f>
         <v>107000</v>
       </c>
-      <c r="L19" s="109">
+      <c r="L19" s="108">
         <f t="shared" si="4"/>
         <v>253115.43172799997</v>
       </c>
-      <c r="M19" s="110">
+      <c r="M19" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N19" s="111">
+      <c r="N19" s="110">
         <f>ROUND(SUM(I19:M19),0) + P19</f>
         <v>340324.09</v>
       </c>
-      <c r="O19" s="112">
+      <c r="O19" s="111">
         <f t="shared" si="2"/>
         <v>350534.09</v>
       </c>
@@ -3786,50 +3795,50 @@
       </c>
     </row>
     <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="104" t="s">
+      <c r="A20" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="104" t="s">
+      <c r="B20" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="104"/>
-      <c r="E20" s="123">
+      <c r="D20" s="103"/>
+      <c r="E20" s="122">
         <v>4.33</v>
       </c>
-      <c r="F20" s="106">
+      <c r="F20" s="105">
         <v>172203.1</v>
       </c>
-      <c r="G20" s="219">
+      <c r="G20" s="113">
         <v>177369</v>
       </c>
-      <c r="H20" s="107" t="s">
+      <c r="H20" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="108">
+      <c r="I20" s="107">
         <f t="shared" si="0"/>
         <v>-5165.8999999999942</v>
       </c>
-      <c r="J20" s="108">
+      <c r="J20" s="107">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K20" s="108"/>
-      <c r="L20" s="109">
+      <c r="K20" s="107"/>
+      <c r="L20" s="108">
         <f t="shared" si="4"/>
         <v>177344.63096799998</v>
       </c>
-      <c r="M20" s="110">
+      <c r="M20" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N20" s="111">
+      <c r="N20" s="110">
         <f t="shared" si="1"/>
         <v>172179.1</v>
       </c>
-      <c r="O20" s="112">
+      <c r="O20" s="111">
         <f t="shared" si="2"/>
         <v>177344.1</v>
       </c>
@@ -3839,52 +3848,52 @@
       </c>
     </row>
     <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="104" t="s">
+      <c r="A21" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="104" t="s">
+      <c r="C21" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="104" t="s">
+      <c r="D21" s="103" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="123">
+      <c r="E21" s="122">
         <v>6.18</v>
       </c>
-      <c r="F21" s="106">
+      <c r="F21" s="105">
         <v>253115.11</v>
       </c>
-      <c r="G21" s="218">
+      <c r="G21" s="151">
         <v>260708.11</v>
       </c>
-      <c r="H21" s="107" t="s">
+      <c r="H21" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="108">
+      <c r="I21" s="212">
         <f t="shared" si="0"/>
         <v>-7593</v>
       </c>
-      <c r="J21" s="108">
+      <c r="J21" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="108"/>
-      <c r="L21" s="109">
+      <c r="K21" s="107"/>
+      <c r="L21" s="108">
         <f t="shared" si="4"/>
         <v>253115.43172799997</v>
       </c>
-      <c r="M21" s="110">
+      <c r="M21" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N21" s="111">
+      <c r="N21" s="110">
         <f t="shared" si="1"/>
         <v>245522.11</v>
       </c>
-      <c r="O21" s="112">
+      <c r="O21" s="111">
         <f t="shared" si="2"/>
         <v>252888.11</v>
       </c>
@@ -3894,50 +3903,50 @@
       </c>
     </row>
     <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="104" t="s">
+      <c r="B22" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="104" t="s">
+      <c r="C22" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="104"/>
-      <c r="E22" s="123">
+      <c r="D22" s="103"/>
+      <c r="E22" s="122">
         <v>4.33</v>
       </c>
-      <c r="F22" s="106">
+      <c r="F22" s="105">
         <v>172061.12</v>
       </c>
-      <c r="G22" s="219">
+      <c r="G22" s="113">
         <v>178000</v>
       </c>
-      <c r="H22" s="107" t="s">
+      <c r="H22" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="108">
+      <c r="I22" s="212">
         <f t="shared" si="0"/>
         <v>-5938.8800000000047</v>
       </c>
-      <c r="J22" s="108">
+      <c r="J22" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K22" s="108"/>
-      <c r="L22" s="109">
+      <c r="K22" s="107"/>
+      <c r="L22" s="108">
         <f t="shared" si="4"/>
         <v>177344.63096799998</v>
       </c>
-      <c r="M22" s="110">
+      <c r="M22" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N22" s="111">
+      <c r="N22" s="110">
         <f t="shared" si="1"/>
         <v>171406.12</v>
       </c>
-      <c r="O22" s="112">
+      <c r="O22" s="111">
         <f t="shared" si="2"/>
         <v>176548.12</v>
       </c>
@@ -3947,54 +3956,55 @@
       </c>
     </row>
     <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="104" t="s">
+      <c r="B23" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="103" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="123">
+      <c r="E23" s="122">
         <v>6.18</v>
       </c>
-      <c r="F23" s="106">
-        <v>253115.13</v>
-      </c>
-      <c r="G23" s="114">
-        <v>0</v>
-      </c>
-      <c r="H23" s="107" t="s">
+      <c r="F23" s="105">
+        <v>260708.13</v>
+      </c>
+      <c r="G23" s="113">
+        <f>F23</f>
+        <v>260708.13</v>
+      </c>
+      <c r="H23" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="108">
+      <c r="I23" s="212">
         <f t="shared" si="0"/>
-        <v>253115.13</v>
-      </c>
-      <c r="J23" s="108">
+        <v>0</v>
+      </c>
+      <c r="J23" s="212">
         <f t="shared" si="3"/>
-        <v>7593.4538999999995</v>
-      </c>
-      <c r="K23" s="108"/>
-      <c r="L23" s="109">
+        <v>0</v>
+      </c>
+      <c r="K23" s="107"/>
+      <c r="L23" s="108">
         <f t="shared" si="4"/>
         <v>253115.43172799997</v>
       </c>
-      <c r="M23" s="110">
+      <c r="M23" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N23" s="111">
+      <c r="N23" s="110">
         <f t="shared" si="1"/>
-        <v>513824.13</v>
-      </c>
-      <c r="O23" s="112">
+        <v>253115.13</v>
+      </c>
+      <c r="O23" s="111">
         <f t="shared" si="2"/>
-        <v>529239.13</v>
+        <v>260708.13</v>
       </c>
       <c r="P23" s="33">
         <f t="shared" si="6"/>
@@ -4002,51 +4012,51 @@
       </c>
     </row>
     <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="104" t="s">
+      <c r="A24" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="104" t="s">
+      <c r="C24" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="104"/>
-      <c r="E24" s="123">
+      <c r="D24" s="103"/>
+      <c r="E24" s="122">
         <v>4.33</v>
       </c>
-      <c r="F24" s="106">
+      <c r="F24" s="105">
         <v>177345.14</v>
       </c>
-      <c r="G24" s="219">
+      <c r="G24" s="113">
         <f>F24</f>
         <v>177345.14</v>
       </c>
-      <c r="H24" s="107" t="s">
+      <c r="H24" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="108">
+      <c r="I24" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="108">
+      <c r="J24" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K24" s="108"/>
-      <c r="L24" s="109">
+      <c r="K24" s="107"/>
+      <c r="L24" s="108">
         <f t="shared" si="4"/>
         <v>177344.63096799998</v>
       </c>
-      <c r="M24" s="110">
+      <c r="M24" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N24" s="111">
+      <c r="N24" s="110">
         <f t="shared" si="1"/>
         <v>177345.14</v>
       </c>
-      <c r="O24" s="112">
+      <c r="O24" s="111">
         <f t="shared" si="2"/>
         <v>182665.14</v>
       </c>
@@ -4056,51 +4066,51 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="113" t="s">
+      <c r="A25" s="112" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="113" t="s">
+      <c r="B25" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="113" t="s">
+      <c r="C25" s="112" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="113"/>
-      <c r="E25" s="124">
+      <c r="D25" s="112"/>
+      <c r="E25" s="123">
         <v>6.18</v>
       </c>
-      <c r="F25" s="114">
+      <c r="F25" s="113">
         <v>253116.15</v>
       </c>
-      <c r="G25" s="219">
+      <c r="G25" s="113">
         <f>462120-G26-G35</f>
         <v>253114.58999999997</v>
       </c>
-      <c r="H25" s="107" t="s">
+      <c r="H25" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="108">
+      <c r="I25" s="212">
         <f t="shared" si="0"/>
         <v>1.5600000000267755</v>
       </c>
-      <c r="J25" s="108">
+      <c r="J25" s="212">
         <f t="shared" si="3"/>
         <v>4.6800000000803262E-2</v>
       </c>
-      <c r="K25" s="108"/>
-      <c r="L25" s="109">
+      <c r="K25" s="107"/>
+      <c r="L25" s="108">
         <f t="shared" si="4"/>
         <v>253115.43172799997</v>
       </c>
-      <c r="M25" s="110">
+      <c r="M25" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N25" s="111">
+      <c r="N25" s="110">
         <f t="shared" si="1"/>
         <v>253117.15</v>
       </c>
-      <c r="O25" s="112">
+      <c r="O25" s="111">
         <f t="shared" si="2"/>
         <v>260711.15</v>
       </c>
@@ -4110,51 +4120,51 @@
       </c>
     </row>
     <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="104" t="s">
+      <c r="A26" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="104" t="s">
+      <c r="B26" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="104" t="s">
+      <c r="C26" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="104"/>
-      <c r="E26" s="123">
+      <c r="D26" s="103"/>
+      <c r="E26" s="122">
         <v>4.33</v>
       </c>
-      <c r="F26" s="106">
+      <c r="F26" s="105">
         <v>177345.16</v>
       </c>
-      <c r="G26" s="219">
+      <c r="G26" s="113">
         <f>F26</f>
         <v>177345.16</v>
       </c>
-      <c r="H26" s="107" t="s">
+      <c r="H26" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="108">
+      <c r="I26" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="108">
+      <c r="J26" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K26" s="108"/>
-      <c r="L26" s="109">
+      <c r="K26" s="107"/>
+      <c r="L26" s="108">
         <f t="shared" si="4"/>
         <v>177344.63096799998</v>
       </c>
-      <c r="M26" s="110">
+      <c r="M26" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N26" s="111">
+      <c r="N26" s="110">
         <f t="shared" si="1"/>
         <v>177345.16</v>
       </c>
-      <c r="O26" s="112">
+      <c r="O26" s="111">
         <f t="shared" si="2"/>
         <v>182665.16</v>
       </c>
@@ -4164,53 +4174,53 @@
       </c>
     </row>
     <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="104" t="s">
+      <c r="A27" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="104" t="s">
+      <c r="B27" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="104" t="s">
+      <c r="C27" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="104" t="s">
+      <c r="D27" s="103" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="123">
+      <c r="E27" s="122">
         <v>6.18</v>
       </c>
-      <c r="F27" s="114">
+      <c r="F27" s="113">
         <v>253115.17</v>
       </c>
-      <c r="G27" s="219">
+      <c r="G27" s="113">
         <f>F27</f>
         <v>253115.17</v>
       </c>
-      <c r="H27" s="107" t="s">
+      <c r="H27" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="108">
+      <c r="I27" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="108">
+      <c r="J27" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K27" s="108"/>
-      <c r="L27" s="109">
+      <c r="K27" s="107"/>
+      <c r="L27" s="108">
         <f t="shared" si="4"/>
         <v>253115.43172799997</v>
       </c>
-      <c r="M27" s="110">
+      <c r="M27" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N27" s="111">
+      <c r="N27" s="110">
         <f t="shared" si="1"/>
         <v>253115.17</v>
       </c>
-      <c r="O27" s="112">
+      <c r="O27" s="111">
         <f t="shared" si="2"/>
         <v>260708.17</v>
       </c>
@@ -4220,51 +4230,51 @@
       </c>
     </row>
     <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="104" t="s">
+      <c r="A28" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="104" t="s">
+      <c r="B28" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="104" t="s">
+      <c r="C28" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="104"/>
-      <c r="E28" s="123">
+      <c r="D28" s="103"/>
+      <c r="E28" s="122">
         <v>4.33</v>
       </c>
-      <c r="F28" s="106">
+      <c r="F28" s="105">
         <v>177345.18</v>
       </c>
-      <c r="G28" s="218">
+      <c r="G28" s="151">
         <f>F28</f>
         <v>177345.18</v>
       </c>
-      <c r="H28" s="107" t="s">
+      <c r="H28" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="108">
+      <c r="I28" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="108">
+      <c r="J28" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K28" s="108"/>
-      <c r="L28" s="109">
+      <c r="K28" s="107"/>
+      <c r="L28" s="108">
         <f t="shared" si="4"/>
         <v>177344.63096799998</v>
       </c>
-      <c r="M28" s="110">
+      <c r="M28" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N28" s="111">
+      <c r="N28" s="110">
         <f t="shared" si="1"/>
         <v>177345.18</v>
       </c>
-      <c r="O28" s="112">
+      <c r="O28" s="111">
         <f t="shared" si="2"/>
         <v>182665.18</v>
       </c>
@@ -4274,49 +4284,49 @@
       </c>
     </row>
     <row r="29" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="212" t="s">
+      <c r="A29" s="188" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="213"/>
-      <c r="C29" s="104" t="s">
+      <c r="B29" s="189"/>
+      <c r="C29" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="104"/>
-      <c r="E29" s="123">
+      <c r="D29" s="103"/>
+      <c r="E29" s="122">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F29" s="106">
+      <c r="F29" s="105">
         <v>31660.19</v>
       </c>
-      <c r="G29" s="219">
+      <c r="G29" s="113">
         <f>F29</f>
         <v>31660.19</v>
       </c>
-      <c r="H29" s="107" t="s">
+      <c r="H29" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="108">
+      <c r="I29" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="108">
+      <c r="J29" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K29" s="108"/>
-      <c r="L29" s="109">
+      <c r="K29" s="107"/>
+      <c r="L29" s="108">
         <f t="shared" si="4"/>
         <v>31659.907560800002</v>
       </c>
-      <c r="M29" s="110">
+      <c r="M29" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N29" s="111">
+      <c r="N29" s="110">
         <f t="shared" si="1"/>
         <v>31660.19</v>
       </c>
-      <c r="O29" s="112">
+      <c r="O29" s="111">
         <f t="shared" si="2"/>
         <v>32610.19</v>
       </c>
@@ -4326,48 +4336,48 @@
       </c>
     </row>
     <row r="30" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="212" t="s">
+      <c r="A30" s="188" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="213"/>
-      <c r="C30" s="113" t="s">
+      <c r="B30" s="189"/>
+      <c r="C30" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="104"/>
-      <c r="E30" s="123">
+      <c r="D30" s="103"/>
+      <c r="E30" s="122">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F30" s="115">
+      <c r="F30" s="114">
         <v>31210.2</v>
       </c>
-      <c r="G30" s="218">
+      <c r="G30" s="151">
         <v>40000.199999999997</v>
       </c>
-      <c r="H30" s="107" t="s">
+      <c r="H30" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I30" s="108">
+      <c r="I30" s="212">
         <f t="shared" si="0"/>
         <v>-8789.9999999999964</v>
       </c>
-      <c r="J30" s="108">
+      <c r="J30" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K30" s="108"/>
-      <c r="L30" s="109">
+      <c r="K30" s="107"/>
+      <c r="L30" s="108">
         <f t="shared" si="4"/>
         <v>31659.907560800002</v>
       </c>
-      <c r="M30" s="110">
+      <c r="M30" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N30" s="111">
+      <c r="N30" s="110">
         <f t="shared" si="1"/>
         <v>22870.2</v>
       </c>
-      <c r="O30" s="112">
+      <c r="O30" s="111">
         <f t="shared" si="2"/>
         <v>23556.2</v>
       </c>
@@ -4377,52 +4387,53 @@
       </c>
     </row>
     <row r="31" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="212" t="s">
+      <c r="A31" s="188" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="213"/>
-      <c r="C31" s="116" t="s">
+      <c r="B31" s="189"/>
+      <c r="C31" s="115" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="104" t="s">
+      <c r="D31" s="103" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="123">
+      <c r="E31" s="122">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F31" s="115">
-        <v>28660.21</v>
-      </c>
-      <c r="G31" s="153">
-        <v>0</v>
-      </c>
-      <c r="H31" s="107" t="s">
+      <c r="F31" s="114">
+        <v>29520.21</v>
+      </c>
+      <c r="G31" s="151">
+        <f>F31</f>
+        <v>29520.21</v>
+      </c>
+      <c r="H31" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I31" s="108">
+      <c r="I31" s="212">
         <f t="shared" si="0"/>
-        <v>28660.21</v>
-      </c>
-      <c r="J31" s="108">
+        <v>0</v>
+      </c>
+      <c r="J31" s="212">
         <f t="shared" si="3"/>
-        <v>859.80629999999996</v>
-      </c>
-      <c r="K31" s="108"/>
-      <c r="L31" s="109">
+        <v>0</v>
+      </c>
+      <c r="K31" s="107"/>
+      <c r="L31" s="108">
         <f t="shared" si="4"/>
         <v>31659.907560800002</v>
       </c>
-      <c r="M31" s="110">
+      <c r="M31" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N31" s="111">
+      <c r="N31" s="110">
         <f t="shared" si="1"/>
-        <v>61180.21</v>
-      </c>
-      <c r="O31" s="112">
+        <v>31660.21</v>
+      </c>
+      <c r="O31" s="111">
         <f t="shared" si="2"/>
-        <v>63015.21</v>
+        <v>32610.21</v>
       </c>
       <c r="P31" s="33">
         <f t="shared" si="6"/>
@@ -4430,49 +4441,49 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="212" t="s">
+      <c r="A32" s="188" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="213"/>
-      <c r="C32" s="104" t="s">
+      <c r="B32" s="189"/>
+      <c r="C32" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="104"/>
-      <c r="E32" s="123">
+      <c r="D32" s="103"/>
+      <c r="E32" s="122">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F32" s="115">
+      <c r="F32" s="114">
         <v>31660.22</v>
       </c>
-      <c r="G32" s="218">
+      <c r="G32" s="151">
         <f t="shared" ref="G32" si="7">F32</f>
         <v>31660.22</v>
       </c>
-      <c r="H32" s="107" t="s">
+      <c r="H32" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I32" s="108">
+      <c r="I32" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="108">
+      <c r="J32" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K32" s="108"/>
-      <c r="L32" s="109">
+      <c r="K32" s="107"/>
+      <c r="L32" s="108">
         <f t="shared" si="4"/>
         <v>31659.907560800002</v>
       </c>
-      <c r="M32" s="110">
+      <c r="M32" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N32" s="111">
+      <c r="N32" s="110">
         <f t="shared" si="1"/>
         <v>31660.22</v>
       </c>
-      <c r="O32" s="112">
+      <c r="O32" s="111">
         <f t="shared" si="2"/>
         <v>32610.22</v>
       </c>
@@ -4482,49 +4493,49 @@
       </c>
     </row>
     <row r="33" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="212" t="s">
+      <c r="A33" s="188" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="213"/>
-      <c r="C33" s="117" t="s">
+      <c r="B33" s="189"/>
+      <c r="C33" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="117"/>
-      <c r="E33" s="123">
+      <c r="D33" s="116"/>
+      <c r="E33" s="122">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F33" s="115">
+      <c r="F33" s="114">
         <v>30682.23</v>
       </c>
-      <c r="G33" s="218">
+      <c r="G33" s="151">
         <f>G32</f>
         <v>31660.22</v>
       </c>
-      <c r="H33" s="107" t="s">
+      <c r="H33" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="I33" s="108">
+      <c r="I33" s="212">
         <f t="shared" si="0"/>
         <v>-977.9900000000016</v>
       </c>
-      <c r="J33" s="108">
+      <c r="J33" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K33" s="108"/>
-      <c r="L33" s="109">
+      <c r="K33" s="107"/>
+      <c r="L33" s="108">
         <f t="shared" si="4"/>
         <v>31659.907560800002</v>
       </c>
-      <c r="M33" s="110">
+      <c r="M33" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N33" s="111">
+      <c r="N33" s="110">
         <f t="shared" si="1"/>
         <v>30682.23</v>
       </c>
-      <c r="O33" s="112">
+      <c r="O33" s="111">
         <f t="shared" si="2"/>
         <v>31602.23</v>
       </c>
@@ -4534,50 +4545,50 @@
       </c>
     </row>
     <row r="34" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="212" t="s">
+      <c r="A34" s="188" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="213"/>
-      <c r="C34" s="117" t="s">
+      <c r="B34" s="189"/>
+      <c r="C34" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="117" t="s">
+      <c r="D34" s="116" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="123">
+      <c r="E34" s="122">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F34" s="115">
+      <c r="F34" s="114">
         <v>31245.24</v>
       </c>
-      <c r="G34" s="218">
+      <c r="G34" s="151">
         <v>32000</v>
       </c>
-      <c r="H34" s="107" t="s">
+      <c r="H34" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I34" s="108">
+      <c r="I34" s="212">
         <f t="shared" si="0"/>
         <v>-754.7599999999984</v>
       </c>
-      <c r="J34" s="108">
+      <c r="J34" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K34" s="108"/>
-      <c r="L34" s="109">
+      <c r="K34" s="107"/>
+      <c r="L34" s="108">
         <f t="shared" si="4"/>
         <v>31659.907560800002</v>
       </c>
-      <c r="M34" s="110">
+      <c r="M34" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N34" s="111">
+      <c r="N34" s="110">
         <f t="shared" si="1"/>
         <v>30905.24</v>
       </c>
-      <c r="O34" s="112">
+      <c r="O34" s="111">
         <f t="shared" si="2"/>
         <v>31832.240000000002</v>
       </c>
@@ -4587,49 +4598,49 @@
       </c>
     </row>
     <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="212" t="s">
+      <c r="A35" s="188" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="213"/>
-      <c r="C35" s="117" t="s">
+      <c r="B35" s="189"/>
+      <c r="C35" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="117"/>
-      <c r="E35" s="105">
+      <c r="D35" s="116"/>
+      <c r="E35" s="104">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F35" s="115">
+      <c r="F35" s="114">
         <v>31660.25</v>
       </c>
-      <c r="G35" s="219">
+      <c r="G35" s="113">
         <f>F35</f>
         <v>31660.25</v>
       </c>
-      <c r="H35" s="107" t="s">
+      <c r="H35" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I35" s="108">
+      <c r="I35" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="108">
+      <c r="J35" s="212">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K35" s="108"/>
-      <c r="L35" s="109">
+      <c r="K35" s="107"/>
+      <c r="L35" s="108">
         <f t="shared" si="4"/>
         <v>31659.907560800002</v>
       </c>
-      <c r="M35" s="110">
+      <c r="M35" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N35" s="111">
+      <c r="N35" s="110">
         <f t="shared" si="1"/>
         <v>31660.25</v>
       </c>
-      <c r="O35" s="112">
+      <c r="O35" s="111">
         <f t="shared" si="2"/>
         <v>32610.25</v>
       </c>
@@ -4639,49 +4650,49 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="214" t="s">
+      <c r="A36" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="214"/>
-      <c r="C36" s="215"/>
-      <c r="D36" s="127"/>
-      <c r="E36" s="118">
+      <c r="B36" s="190"/>
+      <c r="C36" s="191"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="117">
         <f t="shared" ref="E36:M36" si="8">SUM(E11:E35)</f>
         <v>100.00099999999993</v>
       </c>
-      <c r="F36" s="119">
+      <c r="F36" s="118">
         <f t="shared" si="8"/>
-        <v>4153459.2500000009</v>
-      </c>
-      <c r="G36" s="120">
+        <v>4161912.2500000009</v>
+      </c>
+      <c r="G36" s="119">
         <f t="shared" si="8"/>
-        <v>3957376.2300000009</v>
-      </c>
-      <c r="H36" s="120"/>
-      <c r="I36" s="120">
+        <v>4247604.57</v>
+      </c>
+      <c r="H36" s="119"/>
+      <c r="I36" s="119">
         <f t="shared" si="8"/>
-        <v>196083.02000000002</v>
-      </c>
-      <c r="J36" s="121">
+        <v>-85692.319999999978</v>
+      </c>
+      <c r="J36" s="120">
         <f t="shared" si="8"/>
-        <v>8453.3070000000007</v>
-      </c>
-      <c r="K36" s="121"/>
-      <c r="L36" s="121">
+        <v>4.6800000000803262E-2</v>
+      </c>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120">
         <f t="shared" si="8"/>
         <v>4095759.9171895999</v>
       </c>
-      <c r="M36" s="120">
+      <c r="M36" s="119">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N36" s="122">
+      <c r="N36" s="121">
         <f>SUM(N11:N28)</f>
-        <v>4166682.7100000004</v>
-      </c>
-      <c r="O36" s="122">
+        <v>3905973.7100000004</v>
+      </c>
+      <c r="O36" s="121">
         <f>SUM(O11:O35)</f>
-        <v>4539518.2500000009</v>
+        <v>4240582.2500000009</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4690,31 +4701,31 @@
       <c r="F37" t="s">
         <v>109</v>
       </c>
-      <c r="G37" s="134">
+      <c r="G37" s="133">
         <f>SUMIF(H11:H35,"B",G11:G35)</f>
-        <v>3557376.2300000009</v>
+        <v>3847604.5700000008</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="207"/>
-      <c r="B38" s="207"/>
-      <c r="E38" s="208"/>
-      <c r="F38" s="209" t="s">
+      <c r="A38" s="181"/>
+      <c r="B38" s="181"/>
+      <c r="E38" s="182"/>
+      <c r="F38" s="183" t="s">
         <v>110</v>
       </c>
-      <c r="G38" s="134">
+      <c r="G38" s="133">
         <f>SUMIF(H11:H35,"E",G11:G35)</f>
         <v>400000</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="207"/>
-      <c r="B39" s="207"/>
-      <c r="E39" s="208"/>
-      <c r="F39" s="209"/>
-      <c r="G39" s="135">
+      <c r="A39" s="181"/>
+      <c r="B39" s="181"/>
+      <c r="E39" s="182"/>
+      <c r="F39" s="183"/>
+      <c r="G39" s="134">
         <f>SUM(G37:G38)</f>
-        <v>3957376.2300000009</v>
+        <v>4247604.57</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4741,6 +4752,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="A4:O8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="O9:O10"/>
     <mergeCell ref="A38:B39"/>
     <mergeCell ref="E38:E39"/>
     <mergeCell ref="F38:F39"/>
@@ -4757,19 +4781,6 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="A4:O8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="O9:O10"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026/2DE MAYO/Junio/2DEDMAYO-JUNIO.xlsx
+++ b/2026/2DE MAYO/Junio/2DEDMAYO-JUNIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\2DE MAYO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFA353E-FFFC-4A67-8AD0-7030591E5575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280576AE-E4C0-406F-ADDC-449857EBE2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -429,9 +429,6 @@
     <t>Sindicatos mes de JUNIO</t>
   </si>
   <si>
-    <t>CONSORCIO 2 DE JUNIO 2813/15  -  LIQUIDACIÓN DE GASTOS MAYO 2026</t>
-  </si>
-  <si>
     <t>Mes de JUNIO + SAC</t>
   </si>
   <si>
@@ -442,6 +439,9 @@
   </si>
   <si>
     <t>Seguros Integral de Consorcio BERKLEY INTERNATIONAL SEGUROS S.A. Poliza N° 13-228546 - LA POLIZA SE DEBITA LOS PRIMEROS DIAS DE JULIO</t>
+  </si>
+  <si>
+    <t>CONSORCIO 2 DE MAYO 2813/15  -  LIQUIDACIÓN DE GASTOS MAYO 2026</t>
   </si>
 </sst>
 </file>
@@ -1504,6 +1504,37 @@
     <xf numFmtId="44" fontId="2" fillId="12" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="18" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1513,12 +1544,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1543,17 +1568,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1569,12 +1648,6 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1584,79 +1657,6 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2072,11 +2072,11 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="166" t="s">
+      <c r="B1" s="179" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
       <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2090,12 +2090,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="180" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="170"/>
+      <c r="C3" s="180"/>
+      <c r="D3" s="180"/>
+      <c r="E3" s="181"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -2123,7 +2123,7 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2133,49 +2133,49 @@
       <c r="E6" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="172" t="s">
+      <c r="B8" s="183" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="172"/>
+      <c r="C8" s="183"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="172"/>
-      <c r="C9" s="172"/>
+      <c r="B9" s="183"/>
+      <c r="C9" s="183"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="172"/>
-      <c r="C10" s="172"/>
+      <c r="B10" s="183"/>
+      <c r="C10" s="183"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="171" t="s">
+      <c r="A13" s="182" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="171"/>
-      <c r="C13" s="171"/>
-      <c r="D13" s="171"/>
-      <c r="E13" s="171"/>
+      <c r="B13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="171"/>
-      <c r="B14" s="171"/>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="171"/>
+      <c r="A14" s="182"/>
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+      <c r="E14" s="182"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="171"/>
-      <c r="B15" s="171"/>
-      <c r="C15" s="171"/>
-      <c r="D15" s="171"/>
-      <c r="E15" s="171"/>
+      <c r="A15" s="182"/>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
     </row>
     <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="171"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="171"/>
-      <c r="D16" s="171"/>
-      <c r="E16" s="171"/>
+      <c r="A16" s="182"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+      <c r="E16" s="182"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2205,7 +2205,7 @@
         <v>88</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="139">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="213">
+      <c r="D29" s="165">
         <v>184800</v>
       </c>
       <c r="E29" s="5"/>
@@ -2317,10 +2317,10 @@
       <c r="E32" s="90"/>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="167" t="s">
+      <c r="A33" s="173" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="168"/>
+      <c r="B33" s="174"/>
       <c r="C33" s="41"/>
       <c r="D33" s="139">
         <v>45000</v>
@@ -2330,10 +2330,10 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="167"/>
-      <c r="B34" s="168"/>
+      <c r="A34" s="173"/>
+      <c r="B34" s="174"/>
       <c r="C34" s="41"/>
-      <c r="D34" s="214"/>
+      <c r="D34" s="166"/>
       <c r="E34" s="91"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2358,20 +2358,20 @@
       <c r="E36" s="93"/>
     </row>
     <row r="37" spans="1:7" s="30" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="173" t="s">
-        <v>136</v>
-      </c>
-      <c r="B37" s="174"/>
+      <c r="A37" s="184" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" s="185"/>
       <c r="C37" s="42"/>
-      <c r="D37" s="215"/>
-      <c r="E37" s="164"/>
+      <c r="D37" s="175"/>
+      <c r="E37" s="177"/>
     </row>
     <row r="38" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="175"/>
-      <c r="B38" s="176"/>
+      <c r="A38" s="186"/>
+      <c r="B38" s="187"/>
       <c r="C38" s="42"/>
-      <c r="D38" s="216"/>
-      <c r="E38" s="165"/>
+      <c r="D38" s="176"/>
+      <c r="E38" s="178"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
@@ -2550,8 +2550,8 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="177"/>
-      <c r="B53" s="178"/>
+      <c r="A53" s="169"/>
+      <c r="B53" s="170"/>
       <c r="C53" s="5"/>
       <c r="D53" s="144"/>
       <c r="E53" s="136"/>
@@ -2687,22 +2687,22 @@
       <c r="E66" s="72"/>
     </row>
     <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="177"/>
-      <c r="B67" s="178"/>
+      <c r="A67" s="169"/>
+      <c r="B67" s="170"/>
       <c r="C67" s="5"/>
       <c r="D67" s="61"/>
       <c r="E67" s="59"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="177"/>
-      <c r="B68" s="178"/>
+      <c r="A68" s="169"/>
+      <c r="B68" s="170"/>
       <c r="C68" s="5"/>
       <c r="D68" s="61"/>
       <c r="E68" s="59"/>
     </row>
     <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="167"/>
-      <c r="B69" s="168"/>
+      <c r="A69" s="173"/>
+      <c r="B69" s="174"/>
       <c r="C69" s="5"/>
       <c r="D69" s="61"/>
       <c r="E69" s="59"/>
@@ -2718,7 +2718,7 @@
       <c r="A71" s="38"/>
       <c r="B71" s="37"/>
       <c r="C71" s="37"/>
-      <c r="D71" s="217"/>
+      <c r="D71" s="167"/>
       <c r="E71" s="45">
         <f>SUM(D67:D70)</f>
         <v>0</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B74" s="138"/>
       <c r="C74" s="138"/>
-      <c r="D74" s="218"/>
+      <c r="D74" s="168"/>
       <c r="E74" s="148">
         <v>120000</v>
       </c>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B95" s="85">
         <v>-1600000</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="100" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="162" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B100" s="163">
         <v>1600000</v>
@@ -2971,16 +2971,16 @@
     </row>
     <row r="101" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="180" t="s">
+      <c r="A102" s="172" t="s">
         <v>26</v>
       </c>
-      <c r="B102" s="180"/>
-      <c r="C102" s="180"/>
+      <c r="B102" s="172"/>
+      <c r="C102" s="172"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="180"/>
-      <c r="B103" s="180"/>
-      <c r="C103" s="180"/>
+      <c r="A103" s="172"/>
+      <c r="B103" s="172"/>
+      <c r="C103" s="172"/>
     </row>
     <row r="104" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="74"/>
@@ -3010,41 +3010,35 @@
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="179"/>
-      <c r="B108" s="179"/>
-      <c r="C108" s="179"/>
-      <c r="D108" s="179"/>
-      <c r="E108" s="179"/>
+      <c r="A108" s="171"/>
+      <c r="B108" s="171"/>
+      <c r="C108" s="171"/>
+      <c r="D108" s="171"/>
+      <c r="E108" s="171"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="179"/>
-      <c r="B109" s="179"/>
-      <c r="C109" s="179"/>
-      <c r="D109" s="179"/>
-      <c r="E109" s="179"/>
+      <c r="A109" s="171"/>
+      <c r="B109" s="171"/>
+      <c r="C109" s="171"/>
+      <c r="D109" s="171"/>
+      <c r="E109" s="171"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="179"/>
-      <c r="B110" s="179"/>
-      <c r="C110" s="179"/>
-      <c r="D110" s="179"/>
-      <c r="E110" s="179"/>
+      <c r="A110" s="171"/>
+      <c r="B110" s="171"/>
+      <c r="C110" s="171"/>
+      <c r="D110" s="171"/>
+      <c r="E110" s="171"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="179"/>
-      <c r="B111" s="179"/>
-      <c r="C111" s="179"/>
-      <c r="D111" s="179"/>
-      <c r="E111" s="179"/>
+      <c r="A111" s="171"/>
+      <c r="B111" s="171"/>
+      <c r="C111" s="171"/>
+      <c r="D111" s="171"/>
+      <c r="E111" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A108:E111"/>
-    <mergeCell ref="A102:C103"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A69:B69"/>
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="E37:E38"/>
     <mergeCell ref="B1:D1"/>
@@ -3054,6 +3048,12 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A37:B38"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A108:E111"/>
+    <mergeCell ref="A102:C103"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A69:B69"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3089,16 +3089,16 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="188"/>
+      <c r="G1" s="188"/>
+      <c r="H1" s="188"/>
+      <c r="I1" s="188"/>
+      <c r="J1" s="188"/>
+      <c r="K1" s="188"/>
+      <c r="L1" s="188"/>
+      <c r="M1" s="188"/>
+      <c r="N1" s="188"/>
       <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3107,24 +3107,24 @@
       <c r="C2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="185">
-        <v>0</v>
-      </c>
-      <c r="E2" s="185"/>
+      <c r="D2" s="214">
+        <v>0</v>
+      </c>
+      <c r="E2" s="214"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="214"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="M2" s="184">
+      <c r="M2" s="213">
         <f>Q2</f>
         <v>4095718.96</v>
       </c>
-      <c r="N2" s="184"/>
+      <c r="N2" s="213"/>
       <c r="O2" s="43"/>
       <c r="P2" s="21"/>
       <c r="Q2">
@@ -3149,157 +3149,157 @@
       <c r="O3" s="46"/>
     </row>
     <row r="4" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="200" t="str">
+      <c r="A4" s="197" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="B4" s="201"/>
-      <c r="C4" s="201"/>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="201"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
-      <c r="M4" s="201"/>
-      <c r="N4" s="201"/>
-      <c r="O4" s="202"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
+      <c r="K4" s="198"/>
+      <c r="L4" s="198"/>
+      <c r="M4" s="198"/>
+      <c r="N4" s="198"/>
+      <c r="O4" s="199"/>
     </row>
     <row r="5" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="203"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="204"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="204"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="204"/>
-      <c r="L5" s="204"/>
-      <c r="M5" s="204"/>
-      <c r="N5" s="204"/>
-      <c r="O5" s="205"/>
+      <c r="A5" s="200"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="201"/>
+      <c r="K5" s="201"/>
+      <c r="L5" s="201"/>
+      <c r="M5" s="201"/>
+      <c r="N5" s="201"/>
+      <c r="O5" s="202"/>
     </row>
     <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="203"/>
-      <c r="B6" s="204"/>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="204"/>
-      <c r="I6" s="204"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="204"/>
-      <c r="L6" s="204"/>
-      <c r="M6" s="204"/>
-      <c r="N6" s="204"/>
-      <c r="O6" s="205"/>
+      <c r="A6" s="200"/>
+      <c r="B6" s="201"/>
+      <c r="C6" s="201"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="201"/>
+      <c r="F6" s="201"/>
+      <c r="G6" s="201"/>
+      <c r="H6" s="201"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="201"/>
+      <c r="K6" s="201"/>
+      <c r="L6" s="201"/>
+      <c r="M6" s="201"/>
+      <c r="N6" s="201"/>
+      <c r="O6" s="202"/>
     </row>
     <row r="7" spans="1:18" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="203"/>
-      <c r="B7" s="204"/>
-      <c r="C7" s="204"/>
-      <c r="D7" s="204"/>
-      <c r="E7" s="204"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="204"/>
-      <c r="H7" s="204"/>
-      <c r="I7" s="204"/>
-      <c r="J7" s="204"/>
-      <c r="K7" s="204"/>
-      <c r="L7" s="204"/>
-      <c r="M7" s="204"/>
-      <c r="N7" s="204"/>
-      <c r="O7" s="205"/>
+      <c r="A7" s="200"/>
+      <c r="B7" s="201"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="H7" s="201"/>
+      <c r="I7" s="201"/>
+      <c r="J7" s="201"/>
+      <c r="K7" s="201"/>
+      <c r="L7" s="201"/>
+      <c r="M7" s="201"/>
+      <c r="N7" s="201"/>
+      <c r="O7" s="202"/>
     </row>
     <row r="8" spans="1:18" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="206"/>
-      <c r="B8" s="207"/>
-      <c r="C8" s="207"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
-      <c r="H8" s="207"/>
-      <c r="I8" s="207"/>
-      <c r="J8" s="207"/>
-      <c r="K8" s="207"/>
-      <c r="L8" s="207"/>
-      <c r="M8" s="207"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="208"/>
+      <c r="A8" s="203"/>
+      <c r="B8" s="204"/>
+      <c r="C8" s="204"/>
+      <c r="D8" s="204"/>
+      <c r="E8" s="204"/>
+      <c r="F8" s="204"/>
+      <c r="G8" s="204"/>
+      <c r="H8" s="204"/>
+      <c r="I8" s="204"/>
+      <c r="J8" s="204"/>
+      <c r="K8" s="204"/>
+      <c r="L8" s="204"/>
+      <c r="M8" s="204"/>
+      <c r="N8" s="204"/>
+      <c r="O8" s="205"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="192" t="s">
+      <c r="A9" s="189" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="186" t="s">
+      <c r="B9" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="186" t="s">
+      <c r="C9" s="191" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="124"/>
-      <c r="E9" s="186" t="s">
+      <c r="E9" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="192" t="s">
+      <c r="F9" s="189" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="186" t="s">
+      <c r="G9" s="191" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="186" t="s">
+      <c r="H9" s="191" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="196" t="s">
+      <c r="I9" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="189" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="189" t="s">
         <v>112</v>
       </c>
-      <c r="L9" s="192" t="s">
+      <c r="L9" s="189" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="198" t="s">
+      <c r="M9" s="195" t="s">
         <v>48</v>
       </c>
       <c r="N9" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="O9" s="210" t="s">
+      <c r="O9" s="208" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="209"/>
-      <c r="B10" s="187"/>
-      <c r="C10" s="195"/>
+      <c r="A10" s="206"/>
+      <c r="B10" s="207"/>
+      <c r="C10" s="192"/>
       <c r="D10" s="125"/>
-      <c r="E10" s="195"/>
-      <c r="F10" s="193"/>
-      <c r="G10" s="195"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="193"/>
-      <c r="K10" s="193"/>
-      <c r="L10" s="193"/>
-      <c r="M10" s="199"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="194"/>
+      <c r="J10" s="190"/>
+      <c r="K10" s="190"/>
+      <c r="L10" s="190"/>
+      <c r="M10" s="196"/>
       <c r="N10" s="47" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="O10" s="211"/>
+      <c r="O10" s="209"/>
     </row>
     <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103" t="s">
@@ -3872,11 +3872,11 @@
       <c r="H21" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="212">
+      <c r="I21" s="164">
         <f t="shared" si="0"/>
         <v>-7593</v>
       </c>
-      <c r="J21" s="212">
+      <c r="J21" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3925,11 +3925,11 @@
       <c r="H22" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="212">
+      <c r="I22" s="164">
         <f t="shared" si="0"/>
         <v>-5938.8800000000047</v>
       </c>
-      <c r="J22" s="212">
+      <c r="J22" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3981,11 +3981,11 @@
       <c r="H23" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="212">
+      <c r="I23" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="212">
+      <c r="J23" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4035,11 +4035,11 @@
       <c r="H24" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="212">
+      <c r="I24" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="212">
+      <c r="J24" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4089,11 +4089,11 @@
       <c r="H25" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="212">
+      <c r="I25" s="164">
         <f t="shared" si="0"/>
         <v>1.5600000000267755</v>
       </c>
-      <c r="J25" s="212">
+      <c r="J25" s="164">
         <f t="shared" si="3"/>
         <v>4.6800000000803262E-2</v>
       </c>
@@ -4143,11 +4143,11 @@
       <c r="H26" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="212">
+      <c r="I26" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="212">
+      <c r="J26" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4199,11 +4199,11 @@
       <c r="H27" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="212">
+      <c r="I27" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="212">
+      <c r="J27" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4253,11 +4253,11 @@
       <c r="H28" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="212">
+      <c r="I28" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="212">
+      <c r="J28" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4284,10 +4284,10 @@
       </c>
     </row>
     <row r="29" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="188" t="s">
+      <c r="A29" s="215" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="189"/>
+      <c r="B29" s="216"/>
       <c r="C29" s="103" t="s">
         <v>77</v>
       </c>
@@ -4305,11 +4305,11 @@
       <c r="H29" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="212">
+      <c r="I29" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="212">
+      <c r="J29" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4336,10 +4336,10 @@
       </c>
     </row>
     <row r="30" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="188" t="s">
+      <c r="A30" s="215" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="189"/>
+      <c r="B30" s="216"/>
       <c r="C30" s="112" t="s">
         <v>57</v>
       </c>
@@ -4356,11 +4356,11 @@
       <c r="H30" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I30" s="212">
+      <c r="I30" s="164">
         <f t="shared" si="0"/>
         <v>-8789.9999999999964</v>
       </c>
-      <c r="J30" s="212">
+      <c r="J30" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4387,10 +4387,10 @@
       </c>
     </row>
     <row r="31" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="188" t="s">
+      <c r="A31" s="215" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="189"/>
+      <c r="B31" s="216"/>
       <c r="C31" s="115" t="s">
         <v>79</v>
       </c>
@@ -4410,11 +4410,11 @@
       <c r="H31" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I31" s="212">
+      <c r="I31" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J31" s="212">
+      <c r="J31" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4441,10 +4441,10 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="188" t="s">
+      <c r="A32" s="215" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="189"/>
+      <c r="B32" s="216"/>
       <c r="C32" s="103" t="s">
         <v>63</v>
       </c>
@@ -4462,11 +4462,11 @@
       <c r="H32" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I32" s="212">
+      <c r="I32" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="212">
+      <c r="J32" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
       </c>
     </row>
     <row r="33" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="188" t="s">
+      <c r="A33" s="215" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="189"/>
+      <c r="B33" s="216"/>
       <c r="C33" s="116" t="s">
         <v>66</v>
       </c>
@@ -4514,11 +4514,11 @@
       <c r="H33" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="I33" s="212">
+      <c r="I33" s="164">
         <f t="shared" si="0"/>
         <v>-977.9900000000016</v>
       </c>
-      <c r="J33" s="212">
+      <c r="J33" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4545,10 +4545,10 @@
       </c>
     </row>
     <row r="34" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="188" t="s">
+      <c r="A34" s="215" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="189"/>
+      <c r="B34" s="216"/>
       <c r="C34" s="116" t="s">
         <v>69</v>
       </c>
@@ -4567,11 +4567,11 @@
       <c r="H34" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I34" s="212">
+      <c r="I34" s="164">
         <f t="shared" si="0"/>
         <v>-754.7599999999984</v>
       </c>
-      <c r="J34" s="212">
+      <c r="J34" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4598,10 +4598,10 @@
       </c>
     </row>
     <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="188" t="s">
+      <c r="A35" s="215" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="189"/>
+      <c r="B35" s="216"/>
       <c r="C35" s="116" t="s">
         <v>75</v>
       </c>
@@ -4619,11 +4619,11 @@
       <c r="H35" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="I35" s="212">
+      <c r="I35" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="212">
+      <c r="J35" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4650,11 +4650,11 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="190" t="s">
+      <c r="A36" s="217" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="190"/>
-      <c r="C36" s="191"/>
+      <c r="B36" s="217"/>
+      <c r="C36" s="218"/>
       <c r="D36" s="126"/>
       <c r="E36" s="117">
         <f t="shared" ref="E36:M36" si="8">SUM(E11:E35)</f>
@@ -4707,10 +4707,10 @@
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="181"/>
-      <c r="B38" s="181"/>
-      <c r="E38" s="182"/>
-      <c r="F38" s="183" t="s">
+      <c r="A38" s="210"/>
+      <c r="B38" s="210"/>
+      <c r="E38" s="211"/>
+      <c r="F38" s="212" t="s">
         <v>110</v>
       </c>
       <c r="G38" s="133">
@@ -4719,10 +4719,10 @@
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="181"/>
-      <c r="B39" s="181"/>
-      <c r="E39" s="182"/>
-      <c r="F39" s="183"/>
+      <c r="A39" s="210"/>
+      <c r="B39" s="210"/>
+      <c r="E39" s="211"/>
+      <c r="F39" s="212"/>
       <c r="G39" s="134">
         <f>SUM(G37:G38)</f>
         <v>4247604.57</v>
@@ -4752,19 +4752,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="A4:O8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="O9:O10"/>
     <mergeCell ref="A38:B39"/>
     <mergeCell ref="E38:E39"/>
     <mergeCell ref="F38:F39"/>
@@ -4781,6 +4768,19 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="K9:K10"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="A4:O8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="O9:O10"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
